--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רמי - מלכת הדור קאבר</v>
+        <v>אביחיל איטח - אנא בכח קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410411&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410439&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רמי - מלכת הדור קאבר</v>
+        <v>אביחיל איטח - אנא בכח קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רונן לוגסי - רחקי מכולם קאבר</v>
+        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410410&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410433&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,164 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רונן לוגסי - רחקי מכולם קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רונן לוגסי - לא אבגוד יותר ילדה קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410409&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רונן לוגסי - לא אבגוד יותר ילדה קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נהוראי מלאכי - לב לבן קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410408&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נהוראי מלאכי - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יהונתן לוי - לב לבן קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410407&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יהונתן לוי - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אייל אלוש - סתכלי למעלה קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410406&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אייל אלוש - סתכלי למעלה קאבר</v>
+        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביחיל איטח - אנא בכח קאבר</v>
+        <v>שחר יעקב - בית מזכוכית - גרסת היוצר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410439&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410462&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביחיל איטח - אנא בכח קאבר</v>
+        <v>שחר יעקב - בית מזכוכית - גרסת היוצר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
+        <v>לינוי אוחנה - הכל שתיקות קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410433&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410461&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,316 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
+        <v>לינוי אוחנה - הכל שתיקות קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יקיר יהודה יאיר - השב זכה וברה - גרסה ווקאלית</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410460&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יקיר יהודה יאיר - השב זכה וברה - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יוסי בר - יום חדש עולה על צה''ל קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410459&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יוסי בר - יום חדש עולה על צה''ל קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>חמוטל - בדד קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410458&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>חמוטל - בדד קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אלרום יעקב - התמונות שבאלבום קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410457&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אלרום יעקב - התמונות שבאלבום קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלעד אביבי - אין לי בט איתך קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410456&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלעד אביבי - אין לי בט איתך קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אליה לוי - הלוואי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410455&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אליה לוי - הלוואי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אור חרזי - שיר בעיפרון קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410454&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אור חרזי - שיר בעיפרון קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אופיר לוי &amp; ינאי בן חמו - כמה אהבה &amp; קחי אותי אלייך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410453&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אופיר לוי &amp; ינאי בן חמו - כמה אהבה &amp; קחי אותי אלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>